--- a/data/stocks/USStocks.xlsx
+++ b/data/stocks/USStocks.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J38"/>
+  <dimension ref="A1:K38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -475,6 +475,11 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>Year</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Z-Score</t>
         </is>
       </c>
@@ -501,7 +506,10 @@
         <v>291.87</v>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="n">
+        <v>1988</v>
+      </c>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -530,6 +538,9 @@
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
+        <v>1989</v>
+      </c>
+      <c r="K3" t="n">
         <v>1.096740367296172</v>
       </c>
     </row>
@@ -560,6 +571,9 @@
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
+        <v>1990</v>
+      </c>
+      <c r="K4" t="n">
         <v>-0.9081320691605009</v>
       </c>
     </row>
@@ -590,6 +604,9 @@
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
+        <v>1991</v>
+      </c>
+      <c r="K5" t="n">
         <v>1.026412164071957</v>
       </c>
     </row>
@@ -620,6 +637,9 @@
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
+        <v>1992</v>
+      </c>
+      <c r="K6" t="n">
         <v>-0.29016706811587</v>
       </c>
     </row>
@@ -650,6 +670,9 @@
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
+        <v>1993</v>
+      </c>
+      <c r="K7" t="n">
         <v>-0.1484387962299031</v>
       </c>
     </row>
@@ -680,6 +703,9 @@
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
+        <v>1994</v>
+      </c>
+      <c r="K8" t="n">
         <v>-0.6531548748095825</v>
       </c>
     </row>
@@ -710,6 +736,9 @@
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
+        <v>1995</v>
+      </c>
+      <c r="K9" t="n">
         <v>1.436256625994782</v>
       </c>
     </row>
@@ -740,6 +769,9 @@
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
+        <v>1996</v>
+      </c>
+      <c r="K10" t="n">
         <v>0.5938856464386671</v>
       </c>
     </row>
@@ -770,6 +802,9 @@
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
+        <v>1997</v>
+      </c>
+      <c r="K11" t="n">
         <v>1.193392663631515</v>
       </c>
     </row>
@@ -800,6 +835,9 @@
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
+        <v>1998</v>
+      </c>
+      <c r="K12" t="n">
         <v>0.917652398466368</v>
       </c>
     </row>
@@ -830,6 +868,9 @@
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
+        <v>1999</v>
+      </c>
+      <c r="K13" t="n">
         <v>0.4833163875675585</v>
       </c>
     </row>
@@ -860,6 +901,9 @@
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="K14" t="n">
         <v>-1.253906638962151</v>
       </c>
     </row>
@@ -890,6 +934,9 @@
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
+        <v>2001</v>
+      </c>
+      <c r="K15" t="n">
         <v>-1.414190860895805</v>
       </c>
     </row>
@@ -920,6 +967,9 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="n">
+        <v>2002</v>
+      </c>
+      <c r="K16" t="n">
         <v>-2.002835155778128</v>
       </c>
     </row>
@@ -952,6 +1002,9 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>2003</v>
+      </c>
+      <c r="K17" t="n">
         <v>0.9237608789168489</v>
       </c>
     </row>
@@ -984,6 +1037,9 @@
         <v>0</v>
       </c>
       <c r="J18" t="n">
+        <v>2004</v>
+      </c>
+      <c r="K18" t="n">
         <v>-0.1021411245891835</v>
       </c>
     </row>
@@ -1016,6 +1072,9 @@
         <v>0</v>
       </c>
       <c r="J19" t="n">
+        <v>2005</v>
+      </c>
+      <c r="K19" t="n">
         <v>-0.4461811164515933</v>
       </c>
     </row>
@@ -1046,6 +1105,9 @@
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
+        <v>2006</v>
+      </c>
+      <c r="K20" t="n">
         <v>0.1809350798339466</v>
       </c>
     </row>
@@ -1076,6 +1138,9 @@
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
+        <v>2007</v>
+      </c>
+      <c r="K21" t="n">
         <v>-0.41264210114801</v>
       </c>
     </row>
@@ -1106,6 +1171,9 @@
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
+        <v>2008</v>
+      </c>
+      <c r="K22" t="n">
         <v>-2.861324455919143</v>
       </c>
     </row>
@@ -1136,6 +1204,9 @@
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
+        <v>2009</v>
+      </c>
+      <c r="K23" t="n">
         <v>0.7958285525011189</v>
       </c>
     </row>
@@ -1166,6 +1237,9 @@
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
+        <v>2010</v>
+      </c>
+      <c r="K24" t="n">
         <v>0.1388153783126596</v>
       </c>
     </row>
@@ -1196,6 +1270,9 @@
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
+        <v>2011</v>
+      </c>
+      <c r="K25" t="n">
         <v>-0.6075487292575965</v>
       </c>
     </row>
@@ -1226,6 +1303,9 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
+        <v>2012</v>
+      </c>
+      <c r="K26" t="n">
         <v>0.1929906846475371</v>
       </c>
     </row>
@@ -1256,6 +1336,9 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
+        <v>2013</v>
+      </c>
+      <c r="K27" t="n">
         <v>1.137188880769685</v>
       </c>
     </row>
@@ -1286,6 +1369,9 @@
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
+        <v>2014</v>
+      </c>
+      <c r="K28" t="n">
         <v>0.05958377669599881</v>
       </c>
     </row>
@@ -1316,6 +1402,9 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
+        <v>2015</v>
+      </c>
+      <c r="K29" t="n">
         <v>-0.6495013119741061</v>
       </c>
     </row>
@@ -1346,6 +1435,9 @@
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
+        <v>2016</v>
+      </c>
+      <c r="K30" t="n">
         <v>-0.04003055638608723</v>
       </c>
     </row>
@@ -1376,6 +1468,9 @@
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
+        <v>2017</v>
+      </c>
+      <c r="K31" t="n">
         <v>0.5288476177932651</v>
       </c>
     </row>
@@ -1406,6 +1501,9 @@
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
+        <v>2018</v>
+      </c>
+      <c r="K32" t="n">
         <v>-0.9819063773935718</v>
       </c>
     </row>
@@ -1436,6 +1534,9 @@
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
+        <v>2019</v>
+      </c>
+      <c r="K33" t="n">
         <v>1.085226457918756</v>
       </c>
     </row>
@@ -1466,6 +1567,9 @@
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
+        <v>2020</v>
+      </c>
+      <c r="K34" t="n">
         <v>0.3310250546761849</v>
       </c>
     </row>
@@ -1496,6 +1600,9 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
+        <v>2021</v>
+      </c>
+      <c r="K35" t="n">
         <v>0.9249652868547265</v>
       </c>
     </row>
@@ -1526,6 +1633,9 @@
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="K36" t="n">
         <v>-1.772925782143805</v>
       </c>
     </row>
@@ -1556,6 +1666,9 @@
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="n">
+        <v>2023</v>
+      </c>
+      <c r="K37" t="n">
         <v>0.7856343054097031</v>
       </c>
     </row>
@@ -1586,6 +1699,9 @@
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="J38" t="n">
+        <v>2024</v>
+      </c>
+      <c r="K38" t="n">
         <v>0.7125688114175842</v>
       </c>
     </row>

--- a/data/stocks/USStocks.xlsx
+++ b/data/stocks/USStocks.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:L36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,1229 +480,1279 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>Log_return</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>Z-Score</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>32508</v>
+        <v>32873</v>
       </c>
       <c r="C2" t="n">
-        <v>288.116</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+        <v>379.409</v>
+      </c>
+      <c r="D2" t="n">
+        <v>91.29300000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.316862</v>
+      </c>
       <c r="F2" t="n">
-        <v>256.015</v>
+        <v>285.65</v>
       </c>
       <c r="G2" t="n">
-        <v>242.869</v>
+        <v>285.65</v>
       </c>
       <c r="H2" t="n">
-        <v>291.87</v>
+        <v>383.339</v>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="n">
-        <v>1988</v>
-      </c>
-      <c r="K2" t="inlineStr"/>
+        <v>1989</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.9947106204054655</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>32873</v>
+        <v>33238</v>
       </c>
       <c r="C3" t="n">
-        <v>379.409</v>
+        <v>367.6313</v>
       </c>
       <c r="D3" t="n">
-        <v>91.29300000000001</v>
+        <v>-11.7777</v>
       </c>
       <c r="E3" t="n">
-        <v>0.316862</v>
+        <v>-0.031042</v>
       </c>
       <c r="F3" t="n">
-        <v>285.65</v>
+        <v>386.1619</v>
       </c>
       <c r="G3" t="n">
-        <v>285.65</v>
+        <v>326.0788</v>
       </c>
       <c r="H3" t="n">
-        <v>383.339</v>
+        <v>403.455</v>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="n">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="K3" t="n">
-        <v>1.096740367296172</v>
+        <v>-0.0315</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-0.8039468770576222</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>33238</v>
+        <v>33603</v>
       </c>
       <c r="C4" t="n">
-        <v>367.6313</v>
+        <v>479.6332</v>
       </c>
       <c r="D4" t="n">
-        <v>-11.7777</v>
+        <v>112.0019</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.031042</v>
+        <v>0.304658</v>
       </c>
       <c r="F4" t="n">
-        <v>386.1619</v>
+        <v>363.443</v>
       </c>
       <c r="G4" t="n">
-        <v>326.0788</v>
+        <v>347.0157</v>
       </c>
       <c r="H4" t="n">
-        <v>403.455</v>
+        <v>479.6332</v>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="n">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.9081320691605009</v>
+        <v>0.2659</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.9396018183319552</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>33603</v>
+        <v>33969</v>
       </c>
       <c r="C5" t="n">
-        <v>479.6332</v>
+        <v>516.1779</v>
       </c>
       <c r="D5" t="n">
-        <v>112.0019</v>
+        <v>36.5447</v>
       </c>
       <c r="E5" t="n">
-        <v>0.304658</v>
+        <v>0.076193</v>
       </c>
       <c r="F5" t="n">
-        <v>363.443</v>
+        <v>479.839</v>
       </c>
       <c r="G5" t="n">
-        <v>347.0157</v>
+        <v>457.1601</v>
       </c>
       <c r="H5" t="n">
-        <v>479.6332</v>
+        <v>522.3806</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="n">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="K5" t="n">
-        <v>1.026412164071957</v>
+        <v>0.07340000000000001</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-0.1889560964713187</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>33969</v>
+        <v>34334</v>
       </c>
       <c r="C6" t="n">
-        <v>516.1779</v>
+        <v>568.2021</v>
       </c>
       <c r="D6" t="n">
-        <v>36.5447</v>
+        <v>52.0242</v>
       </c>
       <c r="E6" t="n">
-        <v>0.076193</v>
+        <v>0.100787</v>
       </c>
       <c r="F6" t="n">
-        <v>479.839</v>
+        <v>515.9991</v>
       </c>
       <c r="G6" t="n">
-        <v>457.1601</v>
+        <v>508.6048</v>
       </c>
       <c r="H6" t="n">
-        <v>522.3806</v>
+        <v>573.6017000000001</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="n">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.29016706811587</v>
+        <v>0.096</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.05646046595415515</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>34334</v>
+        <v>34699</v>
       </c>
       <c r="C7" t="n">
-        <v>568.2021</v>
+        <v>575.7049</v>
       </c>
       <c r="D7" t="n">
-        <v>52.0242</v>
+        <v>7.5028</v>
       </c>
       <c r="E7" t="n">
-        <v>0.100787</v>
+        <v>0.013204</v>
       </c>
       <c r="F7" t="n">
-        <v>515.9991</v>
+        <v>567.0948</v>
       </c>
       <c r="G7" t="n">
-        <v>508.6048</v>
+        <v>538.3739</v>
       </c>
       <c r="H7" t="n">
-        <v>573.6017000000001</v>
+        <v>590.9272</v>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="J7" t="n">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.1484387962299031</v>
+        <v>0.0131</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.5424731991343702</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>34699</v>
+        <v>35064</v>
       </c>
       <c r="C8" t="n">
-        <v>575.7049</v>
+        <v>792.0419000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5028</v>
+        <v>216.337</v>
       </c>
       <c r="E8" t="n">
-        <v>0.013204</v>
+        <v>0.375778</v>
       </c>
       <c r="F8" t="n">
-        <v>567.0948</v>
+        <v>575.5205999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>538.3739</v>
+        <v>575.5205999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>590.9272</v>
+        <v>798.7597</v>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="n">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6531548748095825</v>
+        <v>0.319</v>
+      </c>
+      <c r="L8" t="n">
+        <v>1.250907923662105</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>35064</v>
+        <v>35430</v>
       </c>
       <c r="C9" t="n">
-        <v>792.0419000000001</v>
+        <v>973.8967</v>
       </c>
       <c r="D9" t="n">
-        <v>216.337</v>
+        <v>181.8548</v>
       </c>
       <c r="E9" t="n">
-        <v>0.375778</v>
+        <v>0.229602</v>
       </c>
       <c r="F9" t="n">
-        <v>575.5205999999999</v>
+        <v>798.2157</v>
       </c>
       <c r="G9" t="n">
-        <v>575.5205999999999</v>
+        <v>770.1103000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>798.7597</v>
+        <v>994.8511999999999</v>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="J9" t="n">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="K9" t="n">
-        <v>1.436256625994782</v>
+        <v>0.2067</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.592533618039208</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>35430</v>
+        <v>35795</v>
       </c>
       <c r="C10" t="n">
-        <v>973.8967</v>
+        <v>1298.8214</v>
       </c>
       <c r="D10" t="n">
-        <v>181.8548</v>
+        <v>324.9247</v>
       </c>
       <c r="E10" t="n">
-        <v>0.229602</v>
+        <v>0.333634</v>
       </c>
       <c r="F10" t="n">
-        <v>798.2157</v>
+        <v>969.0465</v>
       </c>
       <c r="G10" t="n">
-        <v>770.1103000000001</v>
+        <v>969.0465</v>
       </c>
       <c r="H10" t="n">
-        <v>994.8511999999999</v>
+        <v>1315.2774</v>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="n">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="K10" t="n">
-        <v>0.5938856464386671</v>
+        <v>0.2879</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.068579865738043</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="n">
-        <v>35795</v>
+        <v>36160</v>
       </c>
       <c r="C11" t="n">
-        <v>1298.8214</v>
+        <v>1670.0056</v>
       </c>
       <c r="D11" t="n">
-        <v>324.9247</v>
+        <v>371.1842</v>
       </c>
       <c r="E11" t="n">
-        <v>0.333634</v>
+        <v>0.285785</v>
       </c>
       <c r="F11" t="n">
-        <v>969.0465</v>
+        <v>1305.0396</v>
       </c>
       <c r="G11" t="n">
-        <v>969.0465</v>
+        <v>1242.1021</v>
       </c>
       <c r="H11" t="n">
-        <v>1315.2774</v>
+        <v>1687.0335</v>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="K11" t="n">
-        <v>1.193392663631515</v>
+        <v>0.2514</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.854593559814306</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>36160</v>
+        <v>36525</v>
       </c>
       <c r="C12" t="n">
-        <v>1670.0056</v>
+        <v>2021.4006</v>
       </c>
       <c r="D12" t="n">
-        <v>371.1842</v>
+        <v>351.395</v>
       </c>
       <c r="E12" t="n">
-        <v>0.285785</v>
+        <v>0.210415</v>
       </c>
       <c r="F12" t="n">
-        <v>1305.0396</v>
+        <v>1668.5206</v>
       </c>
       <c r="G12" t="n">
-        <v>1242.1021</v>
+        <v>1647.5659</v>
       </c>
       <c r="H12" t="n">
-        <v>1687.0335</v>
+        <v>2021.4006</v>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="n">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.917652398466368</v>
+        <v>0.191</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5004901932994086</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>36525</v>
+        <v>36891</v>
       </c>
       <c r="C13" t="n">
-        <v>2021.4006</v>
+        <v>1837.3647</v>
       </c>
       <c r="D13" t="n">
-        <v>351.395</v>
+        <v>-184.0359</v>
       </c>
       <c r="E13" t="n">
-        <v>0.210415</v>
+        <v>-0.091044</v>
       </c>
       <c r="F13" t="n">
-        <v>1668.5206</v>
+        <v>2002.1132</v>
       </c>
       <c r="G13" t="n">
-        <v>1647.5659</v>
+        <v>1759.6166</v>
       </c>
       <c r="H13" t="n">
-        <v>2021.4006</v>
+        <v>2108.7558</v>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4833163875675585</v>
+        <v>-0.0955</v>
+      </c>
+      <c r="L13" t="n">
+        <v>-1.17915574223897</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>36891</v>
+        <v>37256</v>
       </c>
       <c r="C14" t="n">
-        <v>1837.3647</v>
+        <v>1618.9788</v>
       </c>
       <c r="D14" t="n">
-        <v>-184.0359</v>
+        <v>-218.3859</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.091044</v>
+        <v>-0.118858</v>
       </c>
       <c r="F14" t="n">
-        <v>2002.1132</v>
+        <v>1785.8598</v>
       </c>
       <c r="G14" t="n">
-        <v>1759.6166</v>
+        <v>1356.6089</v>
       </c>
       <c r="H14" t="n">
-        <v>2108.7558</v>
+        <v>1913.1257</v>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.253906638962151</v>
+        <v>-0.1265</v>
+      </c>
+      <c r="L14" t="n">
+        <v>-1.360897536311186</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="n">
-        <v>37256</v>
+        <v>37621</v>
       </c>
       <c r="C15" t="n">
-        <v>1618.9788</v>
+        <v>1261.1763</v>
       </c>
       <c r="D15" t="n">
-        <v>-218.3859</v>
+        <v>-357.8025</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.118858</v>
+        <v>-0.221005</v>
       </c>
       <c r="F15" t="n">
-        <v>1785.8598</v>
+        <v>1628.5061</v>
       </c>
       <c r="G15" t="n">
-        <v>1356.6089</v>
+        <v>1108.9094</v>
       </c>
       <c r="H15" t="n">
-        <v>1913.1257</v>
+        <v>1655.4431</v>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.414190860895805</v>
+        <v>-0.2498</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-2.083760865637127</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="n">
-        <v>37621</v>
+        <v>37986</v>
       </c>
       <c r="C16" t="n">
-        <v>1261.1763</v>
+        <v>1622.9386</v>
       </c>
       <c r="D16" t="n">
-        <v>-357.8025</v>
+        <v>361.7623</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.221005</v>
+        <v>0.286845</v>
       </c>
       <c r="F16" t="n">
-        <v>1628.5061</v>
+        <v>1303.1732</v>
       </c>
       <c r="G16" t="n">
-        <v>1108.9094</v>
+        <v>1152.1524</v>
       </c>
       <c r="H16" t="n">
-        <v>1655.4431</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
+        <v>1622.9386</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
       <c r="J16" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="K16" t="n">
-        <v>-2.002835155778128</v>
+        <v>0.2522</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8592836706290726</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>37986</v>
+        <v>38352</v>
       </c>
       <c r="C17" t="n">
-        <v>1622.9386</v>
+        <v>1799.5477</v>
       </c>
       <c r="D17" t="n">
-        <v>361.7623</v>
+        <v>176.6091</v>
       </c>
       <c r="E17" t="n">
-        <v>0.286845</v>
+        <v>0.108821</v>
       </c>
       <c r="F17" t="n">
-        <v>1303.1732</v>
+        <v>1618.0504</v>
       </c>
       <c r="G17" t="n">
-        <v>1152.1524</v>
+        <v>1567.9472</v>
       </c>
       <c r="H17" t="n">
-        <v>1622.9386</v>
+        <v>1801.9772</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="K17" t="n">
-        <v>0.9237608789168489</v>
+        <v>0.1033</v>
+      </c>
+      <c r="L17" t="n">
+        <v>-0.01366320476940761</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>38352</v>
+        <v>38717</v>
       </c>
       <c r="C18" t="n">
-        <v>1799.5477</v>
+        <v>1887.9409</v>
       </c>
       <c r="D18" t="n">
-        <v>176.6091</v>
+        <v>88.39319999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>0.108821</v>
+        <v>0.04912</v>
       </c>
       <c r="F18" t="n">
-        <v>1618.0504</v>
+        <v>1784.9561</v>
       </c>
       <c r="G18" t="n">
-        <v>1567.9472</v>
+        <v>1697.7435</v>
       </c>
       <c r="H18" t="n">
-        <v>1801.9772</v>
+        <v>1923.4349</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.1021411245891835</v>
+        <v>0.048</v>
+      </c>
+      <c r="L18" t="n">
+        <v>-0.3378671148401663</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>38717</v>
+        <v>39082</v>
       </c>
       <c r="C19" t="n">
-        <v>1887.9409</v>
+        <v>2186.1274</v>
       </c>
       <c r="D19" t="n">
-        <v>88.39319999999999</v>
+        <v>298.1865</v>
       </c>
       <c r="E19" t="n">
-        <v>0.04912</v>
+        <v>0.157943</v>
       </c>
       <c r="F19" t="n">
-        <v>1784.9561</v>
+        <v>1918.9586</v>
       </c>
       <c r="G19" t="n">
-        <v>1697.7435</v>
+        <v>1866.9178</v>
       </c>
       <c r="H19" t="n">
-        <v>1923.4349</v>
-      </c>
-      <c r="I19" t="n">
-        <v>0</v>
-      </c>
+        <v>2199.1531</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="J19" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.4461811164515933</v>
+        <v>0.1466</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2401890430798483</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>39082</v>
+        <v>39447</v>
       </c>
       <c r="C20" t="n">
-        <v>2186.1274</v>
+        <v>2306.2325</v>
       </c>
       <c r="D20" t="n">
-        <v>298.1865</v>
+        <v>120.1051</v>
       </c>
       <c r="E20" t="n">
-        <v>0.157943</v>
+        <v>0.05494</v>
       </c>
       <c r="F20" t="n">
-        <v>1918.9586</v>
+        <v>2183.9215</v>
       </c>
       <c r="G20" t="n">
-        <v>1866.9178</v>
+        <v>2125.3426</v>
       </c>
       <c r="H20" t="n">
-        <v>2199.1531</v>
+        <v>2447.0275</v>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1809350798339466</v>
+        <v>0.0535</v>
+      </c>
+      <c r="L20" t="n">
+        <v>-0.3056226029886442</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>39447</v>
+        <v>40178</v>
       </c>
       <c r="C21" t="n">
-        <v>2306.2325</v>
+        <v>1837.4993</v>
       </c>
       <c r="D21" t="n">
-        <v>120.1051</v>
+        <v>384.5229</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05494</v>
+        <v>0.264645</v>
       </c>
       <c r="F21" t="n">
-        <v>2183.9215</v>
+        <v>1499.1661</v>
       </c>
       <c r="G21" t="n">
-        <v>2125.3426</v>
+        <v>1095.0358</v>
       </c>
       <c r="H21" t="n">
-        <v>2447.0275</v>
+        <v>1857.8883</v>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="n">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.41264210114801</v>
+        <v>0.2348</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.7572737604078937</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B22" s="2" t="n">
-        <v>39813</v>
+        <v>40543</v>
       </c>
       <c r="C22" t="n">
-        <v>1452.9764</v>
+        <v>2114.2886</v>
       </c>
       <c r="D22" t="n">
-        <v>-853.2560999999999</v>
+        <v>276.7893</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.369978</v>
+        <v>0.150634</v>
       </c>
       <c r="F22" t="n">
-        <v>2273.4058</v>
+        <v>1867.063</v>
       </c>
       <c r="G22" t="n">
-        <v>1206.0388</v>
+        <v>1701.8571</v>
       </c>
       <c r="H22" t="n">
-        <v>2273.4139</v>
+        <v>2117.834</v>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="n">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="K22" t="n">
-        <v>-2.861324455919143</v>
+        <v>0.1403</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2032544204135593</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B23" s="2" t="n">
-        <v>40178</v>
+        <v>40908</v>
       </c>
       <c r="C23" t="n">
-        <v>1837.4993</v>
+        <v>2158.9377</v>
       </c>
       <c r="D23" t="n">
-        <v>384.5229</v>
+        <v>44.6491</v>
       </c>
       <c r="E23" t="n">
-        <v>0.264645</v>
+        <v>0.021118</v>
       </c>
       <c r="F23" t="n">
-        <v>1499.1661</v>
+        <v>2138.3003</v>
       </c>
       <c r="G23" t="n">
-        <v>1095.0358</v>
+        <v>1875.9508</v>
       </c>
       <c r="H23" t="n">
-        <v>1857.8883</v>
+        <v>2305.7632</v>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7958285525011189</v>
+        <v>0.0209</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-0.4967446186903934</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B24" s="2" t="n">
-        <v>40543</v>
+        <v>41274</v>
       </c>
       <c r="C24" t="n">
-        <v>2114.2886</v>
+        <v>2504.4431</v>
       </c>
       <c r="D24" t="n">
-        <v>276.7893</v>
+        <v>345.5054</v>
       </c>
       <c r="E24" t="n">
-        <v>0.150634</v>
+        <v>0.160035</v>
       </c>
       <c r="F24" t="n">
-        <v>1867.063</v>
+        <v>2192.3989</v>
       </c>
       <c r="G24" t="n">
-        <v>1701.8571</v>
+        <v>2192.3989</v>
       </c>
       <c r="H24" t="n">
-        <v>2117.834</v>
+        <v>2556.1321</v>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="K24" t="n">
-        <v>0.1388153783126596</v>
+        <v>0.1485</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.2513280562649195</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>40908</v>
+        <v>41639</v>
       </c>
       <c r="C25" t="n">
-        <v>2158.9377</v>
+        <v>3315.5852</v>
       </c>
       <c r="D25" t="n">
-        <v>44.6491</v>
+        <v>811.1421</v>
       </c>
       <c r="E25" t="n">
-        <v>0.021118</v>
+        <v>0.323881</v>
       </c>
       <c r="F25" t="n">
-        <v>2138.3003</v>
+        <v>2568.5525</v>
       </c>
       <c r="G25" t="n">
-        <v>1875.9508</v>
+        <v>2560.1721</v>
       </c>
       <c r="H25" t="n">
-        <v>2305.7632</v>
+        <v>3315.5852</v>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.6075487292575965</v>
+        <v>0.2806</v>
+      </c>
+      <c r="L25" t="n">
+        <v>1.025782604553296</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>41274</v>
+        <v>42004</v>
       </c>
       <c r="C26" t="n">
-        <v>2504.4431</v>
+        <v>3769.4402</v>
       </c>
       <c r="D26" t="n">
-        <v>345.5054</v>
+        <v>453.855</v>
       </c>
       <c r="E26" t="n">
-        <v>0.160035</v>
+        <v>0.136885</v>
       </c>
       <c r="F26" t="n">
-        <v>2192.3989</v>
+        <v>3286.6873</v>
       </c>
       <c r="G26" t="n">
-        <v>2192.3989</v>
+        <v>3127.8652</v>
       </c>
       <c r="H26" t="n">
-        <v>2556.1321</v>
+        <v>3826.9546</v>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="K26" t="n">
-        <v>0.1929906846475371</v>
+        <v>0.1283</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.1329027581920565</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>41639</v>
+        <v>42369</v>
       </c>
       <c r="C27" t="n">
-        <v>3315.5852</v>
+        <v>3821.603</v>
       </c>
       <c r="D27" t="n">
-        <v>811.1421</v>
+        <v>52.1628</v>
       </c>
       <c r="E27" t="n">
-        <v>0.323881</v>
+        <v>0.013838</v>
       </c>
       <c r="F27" t="n">
-        <v>2568.5525</v>
+        <v>3768.6797</v>
       </c>
       <c r="G27" t="n">
-        <v>2560.1721</v>
+        <v>3465.1853</v>
       </c>
       <c r="H27" t="n">
-        <v>3315.5852</v>
+        <v>3939.3489</v>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="n">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="K27" t="n">
-        <v>1.137188880769685</v>
+        <v>0.0137</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-0.5389556160232951</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>42004</v>
+        <v>42735</v>
       </c>
       <c r="C28" t="n">
-        <v>3769.4402</v>
+        <v>4278.6636</v>
       </c>
       <c r="D28" t="n">
-        <v>453.855</v>
+        <v>457.0606</v>
       </c>
       <c r="E28" t="n">
-        <v>0.136885</v>
+        <v>0.119599</v>
       </c>
       <c r="F28" t="n">
-        <v>3286.6873</v>
+        <v>3763.9863</v>
       </c>
       <c r="G28" t="n">
-        <v>3127.8652</v>
+        <v>3428.9856</v>
       </c>
       <c r="H28" t="n">
-        <v>3826.9546</v>
+        <v>4337.8613</v>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="n">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="K28" t="n">
-        <v>0.05958377669599881</v>
+        <v>0.113</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.04320438885964047</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>42369</v>
+        <v>43100</v>
       </c>
       <c r="C29" t="n">
-        <v>3821.603</v>
+        <v>5212.7632</v>
       </c>
       <c r="D29" t="n">
-        <v>52.1628</v>
+        <v>934.0996</v>
       </c>
       <c r="E29" t="n">
-        <v>0.013838</v>
+        <v>0.218316</v>
       </c>
       <c r="F29" t="n">
-        <v>3768.6797</v>
+        <v>4315.0776</v>
       </c>
       <c r="G29" t="n">
-        <v>3465.1853</v>
+        <v>4315.0776</v>
       </c>
       <c r="H29" t="n">
-        <v>3939.3489</v>
+        <v>5242.2847</v>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="n">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.6495013119741061</v>
+        <v>0.1975</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.5385973436693893</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>42735</v>
+        <v>43465</v>
       </c>
       <c r="C30" t="n">
-        <v>4278.6636</v>
+        <v>4984.2173</v>
       </c>
       <c r="D30" t="n">
-        <v>457.0606</v>
+        <v>-228.5459</v>
       </c>
       <c r="E30" t="n">
-        <v>0.119599</v>
+        <v>-0.043844</v>
       </c>
       <c r="F30" t="n">
-        <v>3763.9863</v>
+        <v>5256.2842</v>
       </c>
       <c r="G30" t="n">
-        <v>3428.9856</v>
+        <v>4672.6602</v>
       </c>
       <c r="H30" t="n">
-        <v>4337.8613</v>
+        <v>5794.7222</v>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.04003055638608723</v>
+        <v>-0.0448</v>
+      </c>
+      <c r="L30" t="n">
+        <v>-0.8819199693531212</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>43100</v>
+        <v>43830</v>
       </c>
       <c r="C31" t="n">
-        <v>5212.7632</v>
+        <v>6553.5688</v>
       </c>
       <c r="D31" t="n">
-        <v>934.0996</v>
+        <v>1569.3515</v>
       </c>
       <c r="E31" t="n">
-        <v>0.218316</v>
+        <v>0.314864</v>
       </c>
       <c r="F31" t="n">
-        <v>4315.0776</v>
+        <v>4990.5562</v>
       </c>
       <c r="G31" t="n">
-        <v>4315.0776</v>
+        <v>4868.2959</v>
       </c>
       <c r="H31" t="n">
-        <v>5242.2847</v>
+        <v>6571.0339</v>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="n">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="K31" t="n">
-        <v>0.5288476177932651</v>
+        <v>0.2737</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.9853303987759319</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B32" s="2" t="n">
-        <v>43465</v>
+        <v>44196</v>
       </c>
       <c r="C32" t="n">
-        <v>4984.2173</v>
+        <v>7759.3455</v>
       </c>
       <c r="D32" t="n">
-        <v>-228.5459</v>
+        <v>1205.7767</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.043844</v>
+        <v>0.183988</v>
       </c>
       <c r="F32" t="n">
-        <v>5256.2842</v>
+        <v>6609.2876</v>
       </c>
       <c r="G32" t="n">
-        <v>4672.6602</v>
+        <v>4559.5049</v>
       </c>
       <c r="H32" t="n">
-        <v>5794.7222</v>
+        <v>7759.3455</v>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="n">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.9819063773935718</v>
+        <v>0.1689</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.3709258820414742</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>43830</v>
+        <v>44561</v>
       </c>
       <c r="C33" t="n">
-        <v>6553.5688</v>
+        <v>9986.697899999999</v>
       </c>
       <c r="D33" t="n">
-        <v>1569.3515</v>
+        <v>2227.3524</v>
       </c>
       <c r="E33" t="n">
-        <v>0.314864</v>
+        <v>0.287054</v>
       </c>
       <c r="F33" t="n">
-        <v>4990.5562</v>
+        <v>7645.2691</v>
       </c>
       <c r="G33" t="n">
-        <v>4868.2959</v>
+        <v>7645.2691</v>
       </c>
       <c r="H33" t="n">
-        <v>6571.0339</v>
+        <v>10041.611</v>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="K33" t="n">
-        <v>1.085226457918756</v>
+        <v>0.2524</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.8604561983327645</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>44196</v>
+        <v>44926</v>
       </c>
       <c r="C34" t="n">
-        <v>7759.3455</v>
+        <v>8178.0205</v>
       </c>
       <c r="D34" t="n">
-        <v>1205.7767</v>
+        <v>-1808.6774</v>
       </c>
       <c r="E34" t="n">
-        <v>0.183988</v>
+        <v>-0.181109</v>
       </c>
       <c r="F34" t="n">
-        <v>6609.2876</v>
+        <v>10050.4083</v>
       </c>
       <c r="G34" t="n">
-        <v>4559.5049</v>
+        <v>7588.9008</v>
       </c>
       <c r="H34" t="n">
-        <v>7759.3455</v>
+        <v>10050.4083</v>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="J34" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K34" t="n">
-        <v>0.3310250546761849</v>
+        <v>-0.1998</v>
+      </c>
+      <c r="L34" t="n">
+        <v>-1.790628939714199</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B35" s="2" t="n">
-        <v>44561</v>
+        <v>45291</v>
       </c>
       <c r="C35" t="n">
-        <v>9986.697899999999</v>
+        <v>10327.8281</v>
       </c>
       <c r="D35" t="n">
-        <v>2227.3524</v>
+        <v>2149.8076</v>
       </c>
       <c r="E35" t="n">
-        <v>0.287054</v>
+        <v>0.262876</v>
       </c>
       <c r="F35" t="n">
-        <v>7645.2691</v>
+        <v>8145.604</v>
       </c>
       <c r="G35" t="n">
-        <v>7645.2691</v>
+        <v>8113.1474</v>
       </c>
       <c r="H35" t="n">
-        <v>10041.611</v>
+        <v>10356.593</v>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K35" t="n">
-        <v>0.9249652868547265</v>
+        <v>0.2334</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.7490660664820517</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B36" s="2" t="n">
-        <v>44926</v>
+        <v>45657</v>
       </c>
       <c r="C36" t="n">
-        <v>8178.0205</v>
+        <v>12911.8218</v>
       </c>
       <c r="D36" t="n">
-        <v>-1808.6774</v>
+        <v>2583.9937</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.181109</v>
+        <v>0.250197</v>
       </c>
       <c r="F36" t="n">
-        <v>10050.4083</v>
+        <v>10269.6897</v>
       </c>
       <c r="G36" t="n">
-        <v>7588.9008</v>
+        <v>10154.1953</v>
       </c>
       <c r="H36" t="n">
-        <v>10050.4083</v>
+        <v>13358.4953</v>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.772925782143805</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="2" t="n">
-        <v>45291</v>
-      </c>
-      <c r="C37" t="n">
-        <v>10327.8281</v>
-      </c>
-      <c r="D37" t="n">
-        <v>2149.8076</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0.262876</v>
-      </c>
-      <c r="F37" t="n">
-        <v>8145.604</v>
-      </c>
-      <c r="G37" t="n">
-        <v>8113.1474</v>
-      </c>
-      <c r="H37" t="n">
-        <v>10356.593</v>
-      </c>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="n">
-        <v>2023</v>
-      </c>
-      <c r="K37" t="n">
-        <v>0.7856343054097031</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="2" t="n">
-        <v>45657</v>
-      </c>
-      <c r="C38" t="n">
-        <v>12911.8218</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2583.9937</v>
-      </c>
-      <c r="E38" t="n">
-        <v>0.250197</v>
-      </c>
-      <c r="F38" t="n">
-        <v>10269.6897</v>
-      </c>
-      <c r="G38" t="n">
-        <v>10154.1953</v>
-      </c>
-      <c r="H38" t="n">
-        <v>13358.4953</v>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="n">
-        <v>2024</v>
-      </c>
-      <c r="K38" t="n">
-        <v>0.7125688114175842</v>
+        <v>0.2233</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.6898534174456202</v>
       </c>
     </row>
   </sheetData>
